--- a/daten/IMPEX_Gfeller_nach MA.xlsx
+++ b/daten/IMPEX_Gfeller_nach MA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11023"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stefan/git/overall-campaigns/daten/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1447CEE-C444-674B-A7C1-1E028FD1B389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ABE8D6D-8DDA-2248-ABBD-724BBA9A8935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="19500" activeTab="2" xr2:uid="{CA613293-7C93-DF48-9410-342ED07C3B23}"/>
+    <workbookView xWindow="-20" yWindow="600" windowWidth="22420" windowHeight="23440" activeTab="2" xr2:uid="{CA613293-7C93-DF48-9410-342ED07C3B23}"/>
   </bookViews>
   <sheets>
     <sheet name="Detail1" sheetId="7" r:id="rId1"/>
@@ -28,8 +28,8 @@
   </definedNames>
   <calcPr calcId="191029" iterate="1" iterateCount="1000" forceFullCalc="1"/>
   <pivotCaches>
-    <pivotCache cacheId="28" r:id="rId9"/>
-    <pivotCache cacheId="33" r:id="rId10"/>
+    <pivotCache cacheId="8" r:id="rId9"/>
+    <pivotCache cacheId="12" r:id="rId10"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
@@ -835,10 +835,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Per cent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="52">
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
+  <dxfs count="51">
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
@@ -1183,56 +1180,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Stefan Gfeller" refreshedDate="46324.541947569443" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="12" xr:uid="{B00BBA69-2C82-C248-97F9-E5276AAEF301}">
-  <cacheSource type="worksheet">
-    <worksheetSource name="Table2"/>
-  </cacheSource>
-  <cacheFields count="9">
-    <cacheField name="Futter" numFmtId="0">
-      <sharedItems/>
-    </cacheField>
-    <cacheField name="Phase" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="3" count="3">
-        <n v="1"/>
-        <n v="2"/>
-        <n v="3"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="DM" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="88" maxValue="89.633333333333326"/>
-    </cacheField>
-    <cacheField name="UEG MJ" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="12.46" maxValue="13.2"/>
-    </cacheField>
-    <cacheField name="CP" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="178.9" maxValue="223"/>
-    </cacheField>
-    <cacheField name="N" numFmtId="165">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="28.624000000000002" maxValue="35.68"/>
-    </cacheField>
-    <cacheField name="P" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="4.46" maxValue="6.5"/>
-    </cacheField>
-    <cacheField name="Jahr" numFmtId="1">
-      <sharedItems containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="2013" maxValue="2024"/>
-    </cacheField>
-    <cacheField name="Analyse" numFmtId="0">
-      <sharedItems/>
-    </cacheField>
-  </cacheFields>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition/>
-    </ext>
-    <ext xmlns:xlpdsc="http://schemas.microsoft.com/office/spreadsheetml/2026/pivotDataSourceClean" uri="{F4336242-56EE-4DD3-A5F7-E900642BF6E9}">
-      <xlpdsc:dataSourceClean>1</xlpdsc:dataSourceClean>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Stefan Gfeller" refreshedDate="46324.541947685182" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="10" xr:uid="{746FA58A-5D15-7D48-AA43-67A81D2A6A96}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Stefan Gfeller" refreshedDate="46324.908915624997" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="10" xr:uid="{746FA58A-5D15-7D48-AA43-67A81D2A6A96}">
   <cacheSource type="worksheet">
     <worksheetSource name="Table1"/>
   </cacheSource>
@@ -1384,144 +1332,56 @@
 </pivotCacheDefinition>
 </file>
 
-<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="12">
-  <r>
-    <s v="Starter"/>
-    <x v="0"/>
-    <n v="89.633333333333326"/>
-    <m/>
-    <n v="203.5"/>
-    <n v="32.56"/>
-    <n v="6.4"/>
-    <n v="2024"/>
-    <s v="Labor"/>
-  </r>
-  <r>
-    <s v="Mast"/>
-    <x v="1"/>
-    <n v="89.066666666666663"/>
-    <m/>
-    <n v="191.81"/>
-    <n v="30.689599999999999"/>
-    <n v="6"/>
-    <n v="2024"/>
-    <s v="Labor"/>
-  </r>
-  <r>
-    <s v="End"/>
-    <x v="2"/>
-    <n v="89.2"/>
-    <m/>
-    <n v="189.1"/>
-    <n v="30.256"/>
-    <n v="5.8"/>
-    <n v="2024"/>
-    <s v="Labor"/>
-  </r>
-  <r>
-    <s v="Impex Start"/>
-    <x v="0"/>
-    <n v="88"/>
-    <n v="12.6"/>
-    <n v="210"/>
-    <n v="33.6"/>
-    <n v="6"/>
-    <s v="?"/>
-    <s v="?"/>
-  </r>
-  <r>
-    <s v="Impex Mast"/>
-    <x v="1"/>
-    <n v="88"/>
-    <n v="13"/>
-    <n v="195"/>
-    <n v="31.2"/>
-    <n v="5"/>
-    <s v="?"/>
-    <s v="?"/>
-  </r>
-  <r>
-    <s v="Impex End"/>
-    <x v="2"/>
-    <n v="88"/>
-    <n v="13.2"/>
-    <n v="180"/>
-    <n v="28.8"/>
-    <n v="4.5"/>
-    <s v="?"/>
-    <s v="?"/>
-  </r>
-  <r>
-    <s v="Agroscope Start"/>
-    <x v="0"/>
-    <m/>
-    <n v="12.6"/>
-    <n v="223"/>
-    <n v="35.68"/>
-    <n v="6.5"/>
-    <n v="2013"/>
-    <s v="Hersteller"/>
-  </r>
-  <r>
-    <s v="Agroscope Mast"/>
-    <x v="1"/>
-    <m/>
-    <n v="13"/>
-    <n v="191"/>
-    <n v="30.56"/>
-    <n v="5.6"/>
-    <n v="2013"/>
-    <s v="Hersteller"/>
-  </r>
-  <r>
-    <s v="Agroscope End"/>
-    <x v="2"/>
-    <m/>
-    <n v="13"/>
-    <n v="192"/>
-    <n v="30.72"/>
-    <n v="5.5"/>
-    <n v="2013"/>
-    <s v="Hersteller"/>
-  </r>
-  <r>
-    <s v="Spring Start"/>
-    <x v="0"/>
-    <m/>
-    <n v="12.46"/>
-    <n v="204.4"/>
-    <n v="32.704000000000001"/>
-    <n v="5.89"/>
-    <n v="2024"/>
-    <s v="Hersteller"/>
-  </r>
-  <r>
-    <s v="Spring Mast"/>
-    <x v="1"/>
-    <m/>
-    <n v="12.73"/>
-    <n v="193.6"/>
-    <n v="30.975999999999999"/>
-    <n v="5.03"/>
-    <n v="2024"/>
-    <s v="Hersteller"/>
-  </r>
-  <r>
-    <s v="Spring End"/>
-    <x v="2"/>
-    <m/>
-    <n v="12.86"/>
-    <n v="178.9"/>
-    <n v="28.624000000000002"/>
-    <n v="4.46"/>
-    <n v="2024"/>
-    <s v="Hersteller"/>
-  </r>
-</pivotCacheRecords>
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Stefan Gfeller" refreshedDate="46324.908916319444" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="12" xr:uid="{B00BBA69-2C82-C248-97F9-E5276AAEF301}">
+  <cacheSource type="worksheet">
+    <worksheetSource name="Table2"/>
+  </cacheSource>
+  <cacheFields count="9">
+    <cacheField name="Futter" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Phase" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="3" count="3">
+        <n v="1"/>
+        <n v="2"/>
+        <n v="3"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="DM" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="88" maxValue="89.633333333333326"/>
+    </cacheField>
+    <cacheField name="UEG MJ" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="12.46" maxValue="13.2"/>
+    </cacheField>
+    <cacheField name="CP" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="178.9" maxValue="223"/>
+    </cacheField>
+    <cacheField name="N" numFmtId="165">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="28.624000000000002" maxValue="35.68"/>
+    </cacheField>
+    <cacheField name="P" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="4.46" maxValue="6.5"/>
+    </cacheField>
+    <cacheField name="Jahr" numFmtId="1">
+      <sharedItems containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="2013" maxValue="2024"/>
+    </cacheField>
+    <cacheField name="Analyse" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+    <ext xmlns:xlpdsc="http://schemas.microsoft.com/office/spreadsheetml/2026/pivotDataSourceClean" uri="{F4336242-56EE-4DD3-A5F7-E900642BF6E9}">
+      <xlpdsc:dataSourceClean>1</xlpdsc:dataSourceClean>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
 </file>
 
-<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="10">
   <r>
     <x v="0"/>
@@ -1966,8 +1826,145 @@
 </pivotCacheRecords>
 </file>
 
+<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="12">
+  <r>
+    <s v="Starter"/>
+    <x v="0"/>
+    <n v="89.633333333333326"/>
+    <m/>
+    <n v="203.5"/>
+    <n v="32.56"/>
+    <n v="6.4"/>
+    <n v="2024"/>
+    <s v="Labor"/>
+  </r>
+  <r>
+    <s v="Mast"/>
+    <x v="1"/>
+    <n v="89.066666666666663"/>
+    <m/>
+    <n v="191.81"/>
+    <n v="30.689599999999999"/>
+    <n v="6"/>
+    <n v="2024"/>
+    <s v="Labor"/>
+  </r>
+  <r>
+    <s v="End"/>
+    <x v="2"/>
+    <n v="89.2"/>
+    <m/>
+    <n v="189.1"/>
+    <n v="30.256"/>
+    <n v="5.8"/>
+    <n v="2024"/>
+    <s v="Labor"/>
+  </r>
+  <r>
+    <s v="Impex Start"/>
+    <x v="0"/>
+    <n v="88"/>
+    <n v="12.6"/>
+    <n v="210"/>
+    <n v="33.6"/>
+    <n v="6"/>
+    <s v="?"/>
+    <s v="?"/>
+  </r>
+  <r>
+    <s v="Impex Mast"/>
+    <x v="1"/>
+    <n v="88"/>
+    <n v="13"/>
+    <n v="195"/>
+    <n v="31.2"/>
+    <n v="5"/>
+    <s v="?"/>
+    <s v="?"/>
+  </r>
+  <r>
+    <s v="Impex End"/>
+    <x v="2"/>
+    <n v="88"/>
+    <n v="13.2"/>
+    <n v="180"/>
+    <n v="28.8"/>
+    <n v="4.5"/>
+    <s v="?"/>
+    <s v="?"/>
+  </r>
+  <r>
+    <s v="Agroscope Start"/>
+    <x v="0"/>
+    <m/>
+    <n v="12.6"/>
+    <n v="223"/>
+    <n v="35.68"/>
+    <n v="6.5"/>
+    <n v="2013"/>
+    <s v="Hersteller"/>
+  </r>
+  <r>
+    <s v="Agroscope Mast"/>
+    <x v="1"/>
+    <m/>
+    <n v="13"/>
+    <n v="191"/>
+    <n v="30.56"/>
+    <n v="5.6"/>
+    <n v="2013"/>
+    <s v="Hersteller"/>
+  </r>
+  <r>
+    <s v="Agroscope End"/>
+    <x v="2"/>
+    <m/>
+    <n v="13"/>
+    <n v="192"/>
+    <n v="30.72"/>
+    <n v="5.5"/>
+    <n v="2013"/>
+    <s v="Hersteller"/>
+  </r>
+  <r>
+    <s v="Spring Start"/>
+    <x v="0"/>
+    <m/>
+    <n v="12.46"/>
+    <n v="204.4"/>
+    <n v="32.704000000000001"/>
+    <n v="5.89"/>
+    <n v="2024"/>
+    <s v="Hersteller"/>
+  </r>
+  <r>
+    <s v="Spring Mast"/>
+    <x v="1"/>
+    <m/>
+    <n v="12.73"/>
+    <n v="193.6"/>
+    <n v="30.975999999999999"/>
+    <n v="5.03"/>
+    <n v="2024"/>
+    <s v="Hersteller"/>
+  </r>
+  <r>
+    <s v="Spring End"/>
+    <x v="2"/>
+    <m/>
+    <n v="12.86"/>
+    <n v="178.9"/>
+    <n v="28.624000000000002"/>
+    <n v="4.46"/>
+    <n v="2024"/>
+    <s v="Hersteller"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F347515E-E323-B742-A091-6AA5CC5DDA40}" name="PivotTable1" cacheId="33" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F347515E-E323-B742-A091-6AA5CC5DDA40}" name="PivotTable1" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A44:C47" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="42">
     <pivotField axis="axisRow" showAll="0">
@@ -2061,7 +2058,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9F602962-76CB-584C-B7EA-6ABF87220D94}" name="PivotTable2" cacheId="33" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9F602962-76CB-584C-B7EA-6ABF87220D94}" name="PivotTable2" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A38:E41" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="42">
     <pivotField axis="axisRow" showAll="0">
@@ -2175,7 +2172,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{02E70B6C-B4B2-954B-99F3-3C35E62CF50C}" name="PivotTable2" cacheId="28" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{02E70B6C-B4B2-954B-99F3-3C35E62CF50C}" name="PivotTable2" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A18:C22" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -2228,7 +2225,7 @@
     <dataField name="StdDev of CP" fld="4" subtotal="stdDev" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="4">
+    <format dxfId="3">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
@@ -2283,7 +2280,7 @@
     <tableColumn id="2" xr3:uid="{79F68125-E31A-E445-8F1D-2B9F10A8A8A4}" name="HE"/>
     <tableColumn id="3" xr3:uid="{2A7B69DB-7497-124B-9AE6-699C6D364C98}" name="Season"/>
     <tableColumn id="4" xr3:uid="{3F85F2AE-B886-8448-ADA1-7FF3F951399A}" name="Umtrieb"/>
-    <tableColumn id="5" xr3:uid="{02FAD4EA-E429-FD49-9510-07B01647931A}" name="Einstalldatum" dataDxfId="24"/>
+    <tableColumn id="5" xr3:uid="{02FAD4EA-E429-FD49-9510-07B01647931A}" name="Einstalldatum" dataDxfId="23"/>
     <tableColumn id="6" xr3:uid="{C3AF3567-6D67-864C-BAC7-90158611CB42}" name="Ausstalldatum"/>
     <tableColumn id="7" xr3:uid="{1F925993-619A-DC44-A9ED-9518A80D1513}" name="Mastdauer"/>
     <tableColumn id="8" xr3:uid="{CBEE9C9D-DEAC-DF4A-8B4C-30BA68BDC6FB}" name="Anzahl Tiere eingestallt"/>
@@ -2329,7 +2326,7 @@
     <tableColumn id="2" xr3:uid="{AB03CCED-A524-B149-97A5-37C3F114E9DE}" name="HE"/>
     <tableColumn id="3" xr3:uid="{A3242464-C597-5D4B-9B7D-07289D5EBB7B}" name="Season"/>
     <tableColumn id="4" xr3:uid="{ED1A3289-B407-8B41-A364-BEA490904384}" name="Umtrieb"/>
-    <tableColumn id="5" xr3:uid="{ED22F478-51AE-6644-B668-E49C903C5926}" name="Einstalldatum" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{ED22F478-51AE-6644-B668-E49C903C5926}" name="Einstalldatum" dataDxfId="22"/>
     <tableColumn id="6" xr3:uid="{E9B56D33-3C0C-B949-B666-E4AB28B9C6E1}" name="Ausstalldatum"/>
     <tableColumn id="7" xr3:uid="{1B627AE6-5F06-5040-AA65-3F9638ED96CB}" name="Mastdauer"/>
     <tableColumn id="8" xr3:uid="{92069E07-7202-BB4D-B00F-145E8507427C}" name="Anzahl Tiere eingestallt"/>
@@ -2377,16 +2374,16 @@
     <tableColumn id="1" xr3:uid="{0FF62526-6723-7243-AD3D-6BE0895BDDDF}" name="Stall"/>
     <tableColumn id="30" xr3:uid="{09732289-8F20-684C-81BF-198902DD12E6}" name="HE"/>
     <tableColumn id="34" xr3:uid="{F95FF5CF-C830-D84E-AA3B-02A7C89D9D31}" name="Season"/>
-    <tableColumn id="2" xr3:uid="{E6DECC95-1DC0-4449-9C84-0783B5888F79}" name="Umtrieb" dataDxfId="51"/>
-    <tableColumn id="3" xr3:uid="{7F69C21B-754C-B644-B2F0-BB14490E0AD2}" name="Einstalldatum" dataDxfId="50"/>
-    <tableColumn id="4" xr3:uid="{546F48A0-D81B-FD42-AA19-2806FB7F9454}" name="Ausstalldatum" dataDxfId="49"/>
+    <tableColumn id="2" xr3:uid="{E6DECC95-1DC0-4449-9C84-0783B5888F79}" name="Umtrieb" dataDxfId="50"/>
+    <tableColumn id="3" xr3:uid="{7F69C21B-754C-B644-B2F0-BB14490E0AD2}" name="Einstalldatum" dataDxfId="49"/>
+    <tableColumn id="4" xr3:uid="{546F48A0-D81B-FD42-AA19-2806FB7F9454}" name="Ausstalldatum" dataDxfId="48"/>
     <tableColumn id="5" xr3:uid="{0B1C3FED-CA19-134C-A3DB-A1730A14999C}" name="Mastdauer"/>
     <tableColumn id="6" xr3:uid="{6D194F33-98E9-D34E-8189-67AF5F4916A6}" name="Anzahl Tiere eingestallt"/>
     <tableColumn id="7" xr3:uid="{FE87BA2C-C691-D845-8504-EF1B3DD1EEE7}" name="Anzahl Tiere ausgestallt"/>
     <tableColumn id="8" xr3:uid="{0947B7E5-ABAA-7E41-A5FA-8678370C7F18}" name="Abgänge"/>
     <tableColumn id="9" xr3:uid="{10571F27-463C-5540-B2A1-BEF94A840622}" name="Netto eingestallt_kg"/>
     <tableColumn id="10" xr3:uid="{84EB2BF4-7FE7-C943-9925-1640295C6991}" name="Netto ausgestallt_kg"/>
-    <tableColumn id="40" xr3:uid="{E20CCA3A-D923-834F-A19D-08A1E2EC33EB}" name="LU ausgestallt" dataDxfId="48">
+    <tableColumn id="40" xr3:uid="{E20CCA3A-D923-834F-A19D-08A1E2EC33EB}" name="LU ausgestallt" dataDxfId="47">
       <calculatedColumnFormula>Table1[[#This Row],[Netto ausgestallt_kg]]/500</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="11" xr3:uid="{EAF1917C-DD03-1A48-BADF-EF3A5FA5EDAD}" name="Abgänge Netto_kg"/>
@@ -2394,48 +2391,48 @@
     <tableColumn id="13" xr3:uid="{EC60DED4-5A83-8242-9A3E-FCE95FAEAE36}" name="Futter_2_kg"/>
     <tableColumn id="14" xr3:uid="{33857E3A-2FD3-F043-9201-6F359C0F21F9}" name="Futter_3_kg"/>
     <tableColumn id="15" xr3:uid="{279877AD-B7FC-CD4A-9A3F-72CF54759ADF}" name="Futter_total_kg"/>
-    <tableColumn id="16" xr3:uid="{983355EC-A3AC-7C45-A08C-EB459637EC4D}" name="FV" dataDxfId="47"/>
-    <tableColumn id="17" xr3:uid="{B29F8FE9-D1B7-E64B-B5FD-8FFAED2240D4}" name="N_Futter_1_lg" dataDxfId="46"/>
-    <tableColumn id="18" xr3:uid="{CB8F86B5-9D8F-4346-8DDA-2E351DA0961A}" name="N_Futter_2_kg" dataDxfId="45"/>
-    <tableColumn id="19" xr3:uid="{3BAB8753-64B7-0048-92A8-BF054DB00023}" name="N_Futter_3_kg" dataDxfId="44"/>
-    <tableColumn id="20" xr3:uid="{1F8CAAC7-1C37-1944-AC0A-9D482B07991F}" name="Total N_Futter_kg" dataDxfId="43"/>
-    <tableColumn id="21" xr3:uid="{6101DF9B-C2CF-BA4A-A49C-FED53DB2708D}" name="N_eingestallt_kg" dataDxfId="42"/>
-    <tableColumn id="22" xr3:uid="{7DC028B3-6B9D-F24D-97AD-906B514B29B7}" name="N_geschlachtet_kg" dataDxfId="41"/>
-    <tableColumn id="23" xr3:uid="{5C108F7D-E070-6648-A541-F229E581946F}" name="N_Produziert_kg" dataDxfId="40"/>
-    <tableColumn id="24" xr3:uid="{EFF3C25D-EFD2-F24D-A1E8-3D59A46829D2}" name="N_ausgeschieden_kg" dataDxfId="39"/>
-    <tableColumn id="25" xr3:uid="{52E8B509-BE14-8D43-AD94-32CA263EBA82}" name="N_ausgeschieden pro Tier_g" dataDxfId="38">
-      <calculatedColumnFormula>Table1[[#This Row],[N_ausgeschieden_kg]]/_xlfn.XLOOKUP(Table1[[#This Row],[Umtrieb-Stall]],$F$21:$F$28,$G$21:$G$28,,0,1)*1000</calculatedColumnFormula>
+    <tableColumn id="16" xr3:uid="{983355EC-A3AC-7C45-A08C-EB459637EC4D}" name="FV" dataDxfId="46"/>
+    <tableColumn id="17" xr3:uid="{B29F8FE9-D1B7-E64B-B5FD-8FFAED2240D4}" name="N_Futter_1_lg" dataDxfId="45"/>
+    <tableColumn id="18" xr3:uid="{CB8F86B5-9D8F-4346-8DDA-2E351DA0961A}" name="N_Futter_2_kg" dataDxfId="44"/>
+    <tableColumn id="19" xr3:uid="{3BAB8753-64B7-0048-92A8-BF054DB00023}" name="N_Futter_3_kg" dataDxfId="43"/>
+    <tableColumn id="20" xr3:uid="{1F8CAAC7-1C37-1944-AC0A-9D482B07991F}" name="Total N_Futter_kg" dataDxfId="42"/>
+    <tableColumn id="21" xr3:uid="{6101DF9B-C2CF-BA4A-A49C-FED53DB2708D}" name="N_eingestallt_kg" dataDxfId="41"/>
+    <tableColumn id="22" xr3:uid="{7DC028B3-6B9D-F24D-97AD-906B514B29B7}" name="N_geschlachtet_kg" dataDxfId="40"/>
+    <tableColumn id="23" xr3:uid="{5C108F7D-E070-6648-A541-F229E581946F}" name="N_Produziert_kg" dataDxfId="39"/>
+    <tableColumn id="24" xr3:uid="{EFF3C25D-EFD2-F24D-A1E8-3D59A46829D2}" name="N_ausgeschieden_kg" dataDxfId="38"/>
+    <tableColumn id="25" xr3:uid="{52E8B509-BE14-8D43-AD94-32CA263EBA82}" name="N_ausgeschieden pro Tier_g" dataDxfId="37">
+      <calculatedColumnFormula>Table1[[#This Row],[N_ausgeschieden_kg]]/_xlfn.XLOOKUP(Table1[[#This Row],[Umtrieb-Stall]],$F$21:$F$30,$G$21:$G$30,,0,1)*1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="38" xr3:uid="{F7EA06E0-0509-514B-A4EA-7C3FBF50E90D}" name="TAN" dataDxfId="37">
+    <tableColumn id="38" xr3:uid="{F7EA06E0-0509-514B-A4EA-7C3FBF50E90D}" name="TAN" dataDxfId="36">
       <calculatedColumnFormula>Table1[[#This Row],[N_ausgeschieden pro Tier_g]]*$D$29</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="26" xr3:uid="{AF67686A-2C1F-3D48-9715-9154404331B8}" name="N_Ausscheidung pro Tier und Jahr_g" dataDxfId="36"/>
-    <tableColumn id="35" xr3:uid="{55655CA1-540D-B24E-8AC1-E43CE520A341}" name="TAN2" dataDxfId="35">
+    <tableColumn id="26" xr3:uid="{AF67686A-2C1F-3D48-9715-9154404331B8}" name="N_Ausscheidung pro Tier und Jahr_g" dataDxfId="35"/>
+    <tableColumn id="35" xr3:uid="{55655CA1-540D-B24E-8AC1-E43CE520A341}" name="TAN2" dataDxfId="34">
       <calculatedColumnFormula>Table1[[#This Row],[N_Ausscheidung pro Tier und Jahr_g]]*$D$29</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{A3F7AC4C-D948-3545-AB63-88AC97350058}" name="NH3-N_gemäss Agrammon_g" dataDxfId="34">
+    <tableColumn id="27" xr3:uid="{A3F7AC4C-D948-3545-AB63-88AC97350058}" name="NH3-N_gemäss Agrammon_g" dataDxfId="33">
       <calculatedColumnFormula>AE5*$D$28</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="41" xr3:uid="{408C788A-314E-574E-A9EF-001742DBE675}" name="NH3_gemessen_total" dataDxfId="33"/>
-    <tableColumn id="42" xr3:uid="{E9FB9F59-A355-144B-B901-294F842BB732}" name="NH3_gemessen_per_LU_und_Tag" dataDxfId="32">
+    <tableColumn id="41" xr3:uid="{408C788A-314E-574E-A9EF-001742DBE675}" name="NH3_gemessen_total" dataDxfId="32"/>
+    <tableColumn id="42" xr3:uid="{E9FB9F59-A355-144B-B901-294F842BB732}" name="NH3_gemessen_per_LU_und_Tag" dataDxfId="31">
       <calculatedColumnFormula>Table1[[#This Row],[NH3_gemessen_total]]/Table1[[#This Row],[LU ausgestallt]]/(Table1[[#This Row],[Mastdauer]]-1)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="28" xr3:uid="{533B2972-3709-5747-8984-7A080B4C174C}" name="NH3_gemessen_pro_Tier_g"/>
-    <tableColumn id="31" xr3:uid="{774C7564-59A0-9D46-A882-7888AD5C2DB4}" name="NH3-N_gemessen_pro_Tier_g" dataDxfId="31">
+    <tableColumn id="31" xr3:uid="{774C7564-59A0-9D46-A882-7888AD5C2DB4}" name="NH3-N_gemessen_pro_Tier_g" dataDxfId="30">
       <calculatedColumnFormula>Table1[[#This Row],[NH3_gemessen_pro_Tier_g]]*$D$26</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="29" xr3:uid="{E16B7C70-9ED7-3441-9D73-3C8A9204B6F4}" name="NH3_gemessen_pro Tier und Jahr_g" dataDxfId="30"/>
-    <tableColumn id="32" xr3:uid="{D4608C61-A824-E943-B1F0-5769E7DE1125}" name="NH3-N_gemessen_pro Tier und Jahr_g" dataDxfId="29">
+    <tableColumn id="29" xr3:uid="{E16B7C70-9ED7-3441-9D73-3C8A9204B6F4}" name="NH3_gemessen_pro Tier und Jahr_g" dataDxfId="29"/>
+    <tableColumn id="32" xr3:uid="{D4608C61-A824-E943-B1F0-5769E7DE1125}" name="NH3-N_gemessen_pro Tier und Jahr_g" dataDxfId="28">
       <calculatedColumnFormula>AJ5*$D$23</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="33" xr3:uid="{910CAA9F-A82F-7D4F-853D-F40AEB482217}" name="Anteil NH3-Emission" dataDxfId="28">
+    <tableColumn id="33" xr3:uid="{910CAA9F-A82F-7D4F-853D-F40AEB482217}" name="Anteil NH3-Emission" dataDxfId="27">
       <calculatedColumnFormula>Table1[[#This Row],[NH3-N_gemessen_pro Tier und Jahr_g]]/Table1[[#This Row],[TAN2]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="39" xr3:uid="{C0DAC17F-A10A-A641-A4CA-C31A41BE936C}" name="Column1" dataDxfId="27" dataCellStyle="Per cent">
+    <tableColumn id="39" xr3:uid="{C0DAC17F-A10A-A641-A4CA-C31A41BE936C}" name="Column1" dataDxfId="26" dataCellStyle="Per cent">
       <calculatedColumnFormula>Table1[[#This Row],[NH3-N_gemessen_pro_Tier_g]]/Table1[[#This Row],[TAN]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="36" xr3:uid="{9F36ABC4-3A5D-E745-B271-BBA161CA8398}" name="Umtrieb-Stall" dataDxfId="26"/>
-    <tableColumn id="37" xr3:uid="{ED7BBE0F-FFCA-5944-9E62-26E60EB5D6B2}" name="order" dataDxfId="25"/>
+    <tableColumn id="36" xr3:uid="{9F36ABC4-3A5D-E745-B271-BBA161CA8398}" name="Umtrieb-Stall" dataDxfId="25"/>
+    <tableColumn id="37" xr3:uid="{ED7BBE0F-FFCA-5944-9E62-26E60EB5D6B2}" name="order" dataDxfId="24"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2451,7 +2448,7 @@
     <tableColumn id="1" xr3:uid="{67A5A8A0-80C1-2941-8214-DBADF87875FC}" name="Stall"/>
     <tableColumn id="30" xr3:uid="{EB557493-AAD4-0C46-9A9E-17DCC5602E90}" name="HE"/>
     <tableColumn id="34" xr3:uid="{D511C495-6E09-6F4B-A576-30A95881617D}" name="Season"/>
-    <tableColumn id="2" xr3:uid="{67864841-7D46-874E-959D-D3E9BEEA680A}" name="Umtrieb" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{67864841-7D46-874E-959D-D3E9BEEA680A}" name="Umtrieb" dataDxfId="21"/>
     <tableColumn id="3" xr3:uid="{EAC63DD0-7982-ED42-9A1F-AA3EE7AC6259}" name="Einstalldatum"/>
     <tableColumn id="4" xr3:uid="{7F0ECB2D-89ED-3B4E-83C1-A166B6075E3B}" name="Ausstalldatum"/>
     <tableColumn id="5" xr3:uid="{837381F2-D762-E043-90C4-98ED8DFF799B}" name="Mastdauer"/>
@@ -2471,56 +2468,56 @@
     <tableColumn id="15" xr3:uid="{643B2260-9C92-1244-8446-DDFD04C96616}" name="Futter_total_kg">
       <calculatedColumnFormula>SUM(N5:P5)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{96E42223-F46A-F843-B60D-757F38DAF7EA}" name="FV" dataDxfId="21">
+    <tableColumn id="16" xr3:uid="{96E42223-F46A-F843-B60D-757F38DAF7EA}" name="FV" dataDxfId="20">
       <calculatedColumnFormula>Q5/L5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{6F526568-E4A8-8C4D-8B9C-4A14E18EA821}" name="N_Futter_1_lg" dataDxfId="20">
+    <tableColumn id="17" xr3:uid="{6F526568-E4A8-8C4D-8B9C-4A14E18EA821}" name="N_Futter_1_lg" dataDxfId="19">
       <calculatedColumnFormula>N5*Fumi!$F$12/1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{83D86878-31D6-2A42-876B-1622CB05D4C0}" name="N_Futter_2_kg" dataDxfId="19">
+    <tableColumn id="18" xr3:uid="{83D86878-31D6-2A42-876B-1622CB05D4C0}" name="N_Futter_2_kg" dataDxfId="18">
       <calculatedColumnFormula>O5*Fumi!$F$13/1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{0428B901-7927-2243-824D-FDBD979CB7C8}" name="N_Futter_3_kg" dataDxfId="18">
+    <tableColumn id="19" xr3:uid="{0428B901-7927-2243-824D-FDBD979CB7C8}" name="N_Futter_3_kg" dataDxfId="17">
       <calculatedColumnFormula>P5*Fumi!$F$14/1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{B6C62097-5006-484B-AEA5-E7BFA6B221FD}" name="Total N_Futter_kg" dataDxfId="17">
+    <tableColumn id="20" xr3:uid="{B6C62097-5006-484B-AEA5-E7BFA6B221FD}" name="Total N_Futter_kg" dataDxfId="16">
       <calculatedColumnFormula>SUM(S5:U5)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{6B6FD9A5-8AEB-6C46-B755-2D8D282460AC}" name="N_eingestallt_kg" dataDxfId="16">
+    <tableColumn id="21" xr3:uid="{6B6FD9A5-8AEB-6C46-B755-2D8D282460AC}" name="N_eingestallt_kg" dataDxfId="15">
       <calculatedColumnFormula>K5*Geflügelgehalte!$H$6/1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{9AA34EBA-F958-A344-AAB4-B1E8BAB52E6A}" name="N_geschlachtet_kg" dataDxfId="15">
+    <tableColumn id="22" xr3:uid="{9AA34EBA-F958-A344-AAB4-B1E8BAB52E6A}" name="N_geschlachtet_kg" dataDxfId="14">
       <calculatedColumnFormula>L5*Geflügelgehalte!$H$6/1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{50A737D1-71EE-DF40-AC05-145A7EEA0B29}" name="N_Produziert_kg" dataDxfId="14">
+    <tableColumn id="23" xr3:uid="{50A737D1-71EE-DF40-AC05-145A7EEA0B29}" name="N_Produziert_kg" dataDxfId="13">
       <calculatedColumnFormula>X5-W5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{61DCAD02-6EEB-B143-BBBB-9718FA735E60}" name="N_ausgeschieden_kg" dataDxfId="13">
+    <tableColumn id="24" xr3:uid="{61DCAD02-6EEB-B143-BBBB-9718FA735E60}" name="N_ausgeschieden_kg" dataDxfId="12">
       <calculatedColumnFormula>V5-Y5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="25" xr3:uid="{F468B901-4AA2-DD43-94C7-0F97EE711511}" name="N_ausgeschieden pro Tier_g" dataDxfId="12">
+    <tableColumn id="25" xr3:uid="{F468B901-4AA2-DD43-94C7-0F97EE711511}" name="N_ausgeschieden pro Tier_g" dataDxfId="11">
       <calculatedColumnFormula>Z5/(H5+J5/2)*1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="26" xr3:uid="{6C5CA16F-2748-1441-86B9-89D979BE48D8}" name="N_Ausscheidung pro Tier und Jahr_g" dataDxfId="11">
+    <tableColumn id="26" xr3:uid="{6C5CA16F-2748-1441-86B9-89D979BE48D8}" name="N_Ausscheidung pro Tier und Jahr_g" dataDxfId="10">
       <calculatedColumnFormula>AA5*$D$23</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="35" xr3:uid="{67DFCC9E-130A-4245-A515-2875A2AB615F}" name="TAN" dataDxfId="10">
+    <tableColumn id="35" xr3:uid="{67DFCC9E-130A-4245-A515-2875A2AB615F}" name="TAN" dataDxfId="9">
       <calculatedColumnFormula>Table14[[#This Row],[N_Ausscheidung pro Tier und Jahr_g]]*$D$29</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{52FCB548-9E2F-E54B-844F-B953C907DFEB}" name="NH3-N_gemäss Agrammon_g" dataDxfId="9">
+    <tableColumn id="27" xr3:uid="{52FCB548-9E2F-E54B-844F-B953C907DFEB}" name="NH3-N_gemäss Agrammon_g" dataDxfId="8">
       <calculatedColumnFormula>AC5*$D$28</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="28" xr3:uid="{E2A2DC82-069B-7B47-9F70-AF15D70B3DF6}" name="NH3_gemessen_pro_Tier_g"/>
-    <tableColumn id="31" xr3:uid="{0A72EF04-F53E-4849-9E2C-6B9F8E2F901C}" name="NH3-N_gemessen_pro_Tier_g" dataDxfId="8">
+    <tableColumn id="31" xr3:uid="{0A72EF04-F53E-4849-9E2C-6B9F8E2F901C}" name="NH3-N_gemessen_pro_Tier_g" dataDxfId="7">
       <calculatedColumnFormula>Table14[[#This Row],[NH3_gemessen_pro_Tier_g]]*$D$26</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="29" xr3:uid="{5DD372CE-53C5-034B-9391-F3D6C00E30BA}" name="NH3_gemessen_pro Tier und Jahr_g" dataDxfId="7">
+    <tableColumn id="29" xr3:uid="{5DD372CE-53C5-034B-9391-F3D6C00E30BA}" name="NH3_gemessen_pro Tier und Jahr_g" dataDxfId="6">
       <calculatedColumnFormula>AE5*$D$23</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="32" xr3:uid="{502CD991-4675-B141-81B7-D5C2A42C2054}" name="NH3-N_gemessen_pro Tier und Jahr_g" dataDxfId="6">
+    <tableColumn id="32" xr3:uid="{502CD991-4675-B141-81B7-D5C2A42C2054}" name="NH3-N_gemessen_pro Tier und Jahr_g" dataDxfId="5">
       <calculatedColumnFormula>AF5*$D$23</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="33" xr3:uid="{F2A51909-1A0C-2940-B3F6-1DE61618C463}" name="Anteil NH3-Emission" dataDxfId="5">
+    <tableColumn id="33" xr3:uid="{F2A51909-1A0C-2940-B3F6-1DE61618C463}" name="Anteil NH3-Emission" dataDxfId="4">
       <calculatedColumnFormula>Table14[[#This Row],[NH3-N_gemessen_pro Tier und Jahr_g]]/Table14[[#This Row],[TAN]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2537,11 +2534,11 @@
     <tableColumn id="3" xr3:uid="{17631431-700D-054F-836F-116331C1B299}" name="DM"/>
     <tableColumn id="4" xr3:uid="{4D73AE2F-65AE-A248-9B67-F502268262CD}" name="UEG MJ"/>
     <tableColumn id="5" xr3:uid="{9F3BC49B-32C8-0646-8145-D38D684FB577}" name="CP"/>
-    <tableColumn id="6" xr3:uid="{882B4E31-F1C1-AB4E-9E2F-7D2A05F2141D}" name="N" dataDxfId="3">
+    <tableColumn id="6" xr3:uid="{882B4E31-F1C1-AB4E-9E2F-7D2A05F2141D}" name="N" dataDxfId="2">
       <calculatedColumnFormula>E3/6.25</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{D7CE11BD-B2BA-DF4A-9C9E-D3A67F4AA133}" name="P"/>
-    <tableColumn id="8" xr3:uid="{3B53FE3B-F0B9-EB4E-BC42-0CE6F348C5D1}" name="Jahr" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{3B53FE3B-F0B9-EB4E-BC42-0CE6F348C5D1}" name="Jahr" dataDxfId="1"/>
     <tableColumn id="9" xr3:uid="{B91AFAE1-1D27-C842-B9B9-5E237E1443F3}" name="Analyse"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -4360,7 +4357,7 @@
         <v>295.45057599999996</v>
       </c>
       <c r="AB5" s="3">
-        <f>Table1[[#This Row],[N_ausgeschieden_kg]]/_xlfn.XLOOKUP(Table1[[#This Row],[Umtrieb-Stall]],$F$21:$F$28,$G$21:$G$28,,0,1)*1000</f>
+        <f>Table1[[#This Row],[N_ausgeschieden_kg]]/_xlfn.XLOOKUP(Table1[[#This Row],[Umtrieb-Stall]],$F$21:$F$30,$G$21:$G$30,,0,1)*1000</f>
         <v>35.324076518412241</v>
       </c>
       <c r="AC5" s="3">
@@ -4368,7 +4365,7 @@
         <v>21.194445911047342</v>
       </c>
       <c r="AD5" s="3">
-        <f t="shared" ref="AD5:AD12" si="7">AB5*$D$23</f>
+        <f t="shared" ref="AD5:AD14" si="7">AB5*$D$23</f>
         <v>300.25465040650403</v>
       </c>
       <c r="AE5" s="3">
@@ -4516,7 +4513,7 @@
         <v>287.57226600000001</v>
       </c>
       <c r="AB6" s="3">
-        <f>Table1[[#This Row],[N_ausgeschieden_kg]]/_xlfn.XLOOKUP(Table1[[#This Row],[Umtrieb-Stall]],$F$21:$F$28,$G$21:$G$28,,0,1)*1000</f>
+        <f>Table1[[#This Row],[N_ausgeschieden_kg]]/_xlfn.XLOOKUP(Table1[[#This Row],[Umtrieb-Stall]],$F$21:$F$30,$G$21:$G$30,,0,1)*1000</f>
         <v>33.939840198276883</v>
       </c>
       <c r="AC6" s="3">
@@ -4672,7 +4669,7 @@
         <v>268.98262399999999</v>
       </c>
       <c r="AB7" s="3">
-        <f>Table1[[#This Row],[N_ausgeschieden_kg]]/_xlfn.XLOOKUP(Table1[[#This Row],[Umtrieb-Stall]],$F$21:$F$28,$G$21:$G$28,,0,1)*1000</f>
+        <f>Table1[[#This Row],[N_ausgeschieden_kg]]/_xlfn.XLOOKUP(Table1[[#This Row],[Umtrieb-Stall]],$F$21:$F$30,$G$21:$G$30,,0,1)*1000</f>
         <v>32.560540370415204</v>
       </c>
       <c r="AC7" s="3">
@@ -4828,7 +4825,7 @@
         <v>301.8799019999999</v>
       </c>
       <c r="AB8" s="3">
-        <f>Table1[[#This Row],[N_ausgeschieden_kg]]/_xlfn.XLOOKUP(Table1[[#This Row],[Umtrieb-Stall]],$F$21:$F$28,$G$21:$G$28,,0,1)*1000</f>
+        <f>Table1[[#This Row],[N_ausgeschieden_kg]]/_xlfn.XLOOKUP(Table1[[#This Row],[Umtrieb-Stall]],$F$21:$F$30,$G$21:$G$30,,0,1)*1000</f>
         <v>35.985207056860162</v>
       </c>
       <c r="AC8" s="3">
@@ -4984,7 +4981,7 @@
         <v>258.07276400000001</v>
       </c>
       <c r="AB9" s="3">
-        <f>Table1[[#This Row],[N_ausgeschieden_kg]]/_xlfn.XLOOKUP(Table1[[#This Row],[Umtrieb-Stall]],$F$21:$F$28,$G$21:$G$28,,0,1)*1000</f>
+        <f>Table1[[#This Row],[N_ausgeschieden_kg]]/_xlfn.XLOOKUP(Table1[[#This Row],[Umtrieb-Stall]],$F$21:$F$30,$G$21:$G$30,,0,1)*1000</f>
         <v>31.33852629022465</v>
       </c>
       <c r="AC9" s="3">
@@ -5140,7 +5137,7 @@
         <v>259.94293800000003</v>
       </c>
       <c r="AB10" s="3">
-        <f>Table1[[#This Row],[N_ausgeschieden_kg]]/_xlfn.XLOOKUP(Table1[[#This Row],[Umtrieb-Stall]],$F$21:$F$28,$G$21:$G$28,,0,1)*1000</f>
+        <f>Table1[[#This Row],[N_ausgeschieden_kg]]/_xlfn.XLOOKUP(Table1[[#This Row],[Umtrieb-Stall]],$F$21:$F$30,$G$21:$G$30,,0,1)*1000</f>
         <v>31.56562695810565</v>
       </c>
       <c r="AC10" s="3">
@@ -5296,7 +5293,7 @@
         <v>276.12562800000001</v>
       </c>
       <c r="AB11" s="3">
-        <f>Table1[[#This Row],[N_ausgeschieden_kg]]/_xlfn.XLOOKUP(Table1[[#This Row],[Umtrieb-Stall]],$F$21:$F$28,$G$21:$G$28,,0,1)*1000</f>
+        <f>Table1[[#This Row],[N_ausgeschieden_kg]]/_xlfn.XLOOKUP(Table1[[#This Row],[Umtrieb-Stall]],$F$21:$F$30,$G$21:$G$30,,0,1)*1000</f>
         <v>33.461661173048959</v>
       </c>
       <c r="AC11" s="3">
@@ -5387,7 +5384,7 @@
         <v>266</v>
       </c>
       <c r="K12" s="3">
-        <f t="shared" si="0"/>
+        <f>H12*$D$21</f>
         <v>346</v>
       </c>
       <c r="L12">
@@ -5452,7 +5449,7 @@
         <v>299.66229999999996</v>
       </c>
       <c r="AB12" s="3">
-        <f>Table1[[#This Row],[N_ausgeschieden_kg]]/_xlfn.XLOOKUP(Table1[[#This Row],[Umtrieb-Stall]],$F$21:$F$28,$G$21:$G$28,,0,1)*1000</f>
+        <f>Table1[[#This Row],[N_ausgeschieden_kg]]/_xlfn.XLOOKUP(Table1[[#This Row],[Umtrieb-Stall]],$F$21:$F$30,$G$21:$G$30,,0,1)*1000</f>
         <v>35.742163645038161</v>
       </c>
       <c r="AC12" s="3">
@@ -5551,7 +5548,7 @@
         <v>18120.240000000002</v>
       </c>
       <c r="M13">
-        <f>L13/500</f>
+        <f>Table1[[#This Row],[Netto ausgestallt_kg]]/500</f>
         <v>36.240480000000005</v>
       </c>
       <c r="N13">
@@ -5609,19 +5606,19 @@
         <v>253.68705600000004</v>
       </c>
       <c r="AB13" s="3">
-        <f>AA13/I13*1000</f>
+        <f>Table1[[#This Row],[N_ausgeschieden_kg]]/_xlfn.XLOOKUP(Table1[[#This Row],[Umtrieb-Stall]],$F$21:$F$30,$G$21:$G$30,,0,1)*1000</f>
         <v>29.498494883720934</v>
       </c>
       <c r="AC13" s="3">
-        <f>AB13*$D$29</f>
+        <f>Table1[[#This Row],[N_ausgeschieden pro Tier_g]]*$D$29</f>
         <v>17.69909693023256</v>
       </c>
       <c r="AD13" s="3">
-        <f>AB13*$D$23</f>
+        <f t="shared" si="7"/>
         <v>250.73720651162793</v>
       </c>
       <c r="AE13" s="3">
-        <f>AD13*$D$29</f>
+        <f>Table1[[#This Row],[N_Ausscheidung pro Tier und Jahr_g]]*$D$29</f>
         <v>150.44232390697675</v>
       </c>
       <c r="AF13" s="3">
@@ -5708,7 +5705,7 @@
         <v>18459.240000000002</v>
       </c>
       <c r="M14">
-        <f>L14/500</f>
+        <f>Table1[[#This Row],[Netto ausgestallt_kg]]/500</f>
         <v>36.918480000000002</v>
       </c>
       <c r="N14">
@@ -5766,19 +5763,19 @@
         <v>283.72687599999983</v>
       </c>
       <c r="AB14" s="3">
-        <f>AA14/I14*1000</f>
+        <f>Table1[[#This Row],[N_ausgeschieden_kg]]/_xlfn.XLOOKUP(Table1[[#This Row],[Umtrieb-Stall]],$F$21:$F$30,$G$21:$G$30,,0,1)*1000</f>
         <v>33.841468988549593</v>
       </c>
       <c r="AC14" s="3">
-        <f>AB14*$D$29</f>
+        <f>Table1[[#This Row],[N_ausgeschieden pro Tier_g]]*$D$29</f>
         <v>20.304881393129754</v>
       </c>
       <c r="AD14" s="3">
-        <f>AB14*$D$23</f>
+        <f t="shared" si="7"/>
         <v>287.65248640267157</v>
       </c>
       <c r="AE14" s="3">
-        <f>AD14*$D$29</f>
+        <f>Table1[[#This Row],[N_Ausscheidung pro Tier und Jahr_g]]*$D$29</f>
         <v>172.59149184160293</v>
       </c>
       <c r="AF14" s="3">
